--- a/M2. Statistica & Excel/PraticaW2D1_GGabriele.xlsx
+++ b/M2. Statistica & Excel/PraticaW2D1_GGabriele.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Desktop\Epicode-Dapt0326\M2. Statistica &amp; Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDAB191-B757-43F8-909B-33403C0D8CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B538F657-31A1-4616-86CC-BC285F0D9CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,7 +102,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +117,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -139,10 +145,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -423,251 +430,500 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:H18"/>
+  <dimension ref="C3:CF20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="3" spans="3:84" x14ac:dyDescent="0.25">
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="3:84" x14ac:dyDescent="0.25">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3">
+        <v>55</v>
+      </c>
+      <c r="E4">
+        <v>49</v>
+      </c>
+      <c r="F4">
+        <v>62</v>
+      </c>
+      <c r="G4">
+        <v>42</v>
+      </c>
+      <c r="H4">
+        <v>53</v>
+      </c>
+      <c r="I4">
+        <v>61</v>
+      </c>
+      <c r="J4">
+        <v>37</v>
+      </c>
+      <c r="K4">
+        <v>57</v>
+      </c>
+      <c r="L4">
+        <v>38</v>
+      </c>
+      <c r="M4">
+        <v>42</v>
+      </c>
+      <c r="N4">
+        <v>62</v>
+      </c>
+      <c r="O4">
+        <v>54</v>
+      </c>
+      <c r="P4">
+        <v>63</v>
+      </c>
+      <c r="Q4">
+        <v>43</v>
+      </c>
+      <c r="R4">
+        <v>59</v>
+      </c>
+      <c r="S4">
+        <v>51</v>
+      </c>
+      <c r="T4">
+        <v>61</v>
+      </c>
+      <c r="U4">
+        <v>43</v>
+      </c>
+      <c r="V4">
+        <v>55</v>
+      </c>
+      <c r="W4">
+        <v>58</v>
+      </c>
+      <c r="X4">
+        <v>66</v>
+      </c>
+      <c r="Y4">
+        <v>39</v>
+      </c>
+      <c r="Z4">
+        <v>45</v>
+      </c>
+      <c r="AA4">
+        <v>54</v>
+      </c>
+      <c r="AB4">
+        <v>64</v>
+      </c>
+      <c r="AC4">
+        <v>50</v>
+      </c>
+      <c r="AD4">
+        <v>62</v>
+      </c>
+      <c r="AE4">
+        <v>40</v>
+      </c>
+      <c r="AF4">
+        <v>52</v>
+      </c>
+      <c r="AG4">
+        <v>43</v>
+      </c>
+      <c r="AH4">
+        <v>55</v>
+      </c>
+      <c r="AI4">
+        <v>50</v>
+      </c>
+      <c r="AJ4">
+        <v>57</v>
+      </c>
+      <c r="AK4">
+        <v>47</v>
+      </c>
+      <c r="AL4">
+        <v>50</v>
+      </c>
+      <c r="AM4">
+        <v>49</v>
+      </c>
+      <c r="AN4">
+        <v>55</v>
+      </c>
+      <c r="AO4">
+        <v>48</v>
+      </c>
+      <c r="AP4">
+        <v>49</v>
+      </c>
+      <c r="AQ4">
+        <v>61</v>
+      </c>
+      <c r="AR4">
+        <v>52</v>
+      </c>
+      <c r="AS4">
+        <v>45</v>
+      </c>
+      <c r="AT4">
+        <v>42</v>
+      </c>
+      <c r="AU4">
+        <v>62</v>
+      </c>
+      <c r="AV4">
+        <v>42</v>
+      </c>
+      <c r="AW4">
+        <v>41</v>
+      </c>
+      <c r="AX4">
+        <v>67</v>
+      </c>
+      <c r="AY4">
+        <v>37</v>
+      </c>
+      <c r="AZ4">
+        <v>47</v>
+      </c>
+      <c r="BA4">
+        <v>66</v>
+      </c>
+      <c r="BB4">
+        <v>50</v>
+      </c>
+      <c r="BC4">
+        <v>54</v>
+      </c>
+      <c r="BD4">
+        <v>47</v>
+      </c>
+      <c r="BE4">
+        <v>50</v>
+      </c>
+      <c r="BF4">
+        <v>42</v>
+      </c>
+      <c r="BG4">
+        <v>57</v>
+      </c>
+      <c r="BH4">
+        <v>49</v>
+      </c>
+      <c r="BI4">
+        <v>62</v>
+      </c>
+      <c r="BJ4">
+        <v>54</v>
+      </c>
+      <c r="BK4">
+        <v>64</v>
+      </c>
+      <c r="BL4">
+        <v>41</v>
+      </c>
+      <c r="BM4">
+        <v>65</v>
+      </c>
+      <c r="BN4">
+        <v>39</v>
+      </c>
+      <c r="BO4">
+        <v>50</v>
+      </c>
+      <c r="BP4">
+        <v>67</v>
+      </c>
+      <c r="BQ4">
+        <v>42</v>
+      </c>
+      <c r="BR4">
+        <v>54</v>
+      </c>
+      <c r="BS4">
+        <v>49</v>
+      </c>
+      <c r="BT4">
+        <v>54</v>
+      </c>
+      <c r="BU4">
+        <v>49</v>
+      </c>
+      <c r="BV4">
+        <v>52</v>
+      </c>
+      <c r="BW4">
+        <v>55</v>
+      </c>
+      <c r="BX4">
+        <v>49</v>
+      </c>
+      <c r="BY4">
+        <v>63</v>
+      </c>
+      <c r="BZ4">
+        <v>48</v>
+      </c>
+      <c r="CA4">
+        <v>49</v>
+      </c>
+      <c r="CB4">
+        <v>55</v>
+      </c>
+      <c r="CC4">
+        <v>67</v>
+      </c>
+      <c r="CD4">
+        <v>37</v>
+      </c>
+      <c r="CE4">
+        <v>45</v>
+      </c>
+      <c r="CF4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="3:84" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
         <v>0</v>
       </c>
-      <c r="C3">
+      <c r="D5">
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+    <row r="6" spans="3:84" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
         <v>1</v>
       </c>
-      <c r="C4">
+      <c r="D6">
         <v>9</v>
       </c>
-      <c r="D4">
+      <c r="E6">
         <v>9</v>
       </c>
-      <c r="E4">
+      <c r="F6">
         <v>9</v>
       </c>
-      <c r="F4">
+      <c r="G6">
         <v>9</v>
       </c>
-      <c r="G4">
+      <c r="H6">
         <v>9</v>
       </c>
-      <c r="H4">
+      <c r="I6">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+    <row r="7" spans="3:84" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
         <v>2</v>
       </c>
-      <c r="C5">
+      <c r="D7">
         <v>81</v>
       </c>
-      <c r="D5">
+      <c r="E7">
         <v>81</v>
       </c>
-      <c r="E5">
+      <c r="F7">
         <v>81</v>
       </c>
-      <c r="F5">
+      <c r="G7">
         <v>324</v>
       </c>
-      <c r="G5">
+      <c r="H7">
         <v>324</v>
       </c>
-      <c r="H5">
+      <c r="I7">
         <v>324</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+    <row r="8" spans="3:84" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="1">
+      <c r="D8" s="1">
         <v>0.95</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E8" s="1">
         <v>0.99</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F8" s="1">
         <v>0.9</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G8" s="1">
         <v>0.95</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H8" s="1">
         <v>0.99</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I8" s="1">
         <v>0.9</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+    <row r="9" spans="3:84" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="2">
-        <f>1-C6</f>
+      <c r="D9" s="2">
+        <f>1-D8</f>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="D7" s="2">
-        <f t="shared" ref="D7:E7" si="0">1-D6</f>
+      <c r="E9" s="2">
+        <f t="shared" ref="E9:F9" si="0">1-E8</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F9" s="2">
         <f t="shared" si="0"/>
         <v>9.9999999999999978E-2</v>
       </c>
-      <c r="F7" s="2">
-        <f t="shared" ref="F7" si="1">1-F6</f>
+      <c r="G9" s="2">
+        <f t="shared" ref="G9" si="1">1-G8</f>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="G7" s="2">
-        <f t="shared" ref="G7" si="2">1-G6</f>
+      <c r="H9" s="2">
+        <f t="shared" ref="H9" si="2">1-H8</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="H7" s="2">
-        <f t="shared" ref="H7" si="3">1-H6</f>
+      <c r="I9" s="2">
+        <f t="shared" ref="I9" si="3">1-I8</f>
         <v>9.9999999999999978E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+    <row r="10" spans="3:84" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
         <v>5</v>
       </c>
-      <c r="C8">
-        <f>$C$3</f>
-        <v>52</v>
-      </c>
-      <c r="D8">
-        <f t="shared" ref="D8:H8" si="4">$C$3</f>
-        <v>52</v>
-      </c>
-      <c r="E8">
+      <c r="D10">
+        <f>AVERAGE(4:4)</f>
+        <v>51.851851851851855</v>
+      </c>
+      <c r="E10">
+        <f>AVERAGE(4:4)</f>
+        <v>51.851851851851855</v>
+      </c>
+      <c r="F10">
+        <f>AVERAGE(4:4)</f>
+        <v>51.851851851851855</v>
+      </c>
+      <c r="G10">
+        <f>AVERAGE(4:4)</f>
+        <v>51.851851851851855</v>
+      </c>
+      <c r="H10">
+        <f>AVERAGE(4:4)</f>
+        <v>51.851851851851855</v>
+      </c>
+      <c r="I10">
+        <f>AVERAGE(4:4)</f>
+        <v>51.851851851851855</v>
+      </c>
+    </row>
+    <row r="11" spans="3:84" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" ref="D11:I11" si="4">_xlfn.CONFIDENCE.NORM(D9,D6,D7)</f>
+        <v>1.9599639845400536</v>
+      </c>
+      <c r="E11" s="2">
         <f t="shared" si="4"/>
-        <v>52</v>
-      </c>
-      <c r="F8">
+        <v>2.5758293035488999</v>
+      </c>
+      <c r="F11" s="2">
         <f t="shared" si="4"/>
-        <v>52</v>
-      </c>
-      <c r="G8">
+        <v>1.6448536269514715</v>
+      </c>
+      <c r="G11" s="2">
         <f t="shared" si="4"/>
-        <v>52</v>
-      </c>
-      <c r="H8">
+        <v>0.9799819922700268</v>
+      </c>
+      <c r="H11" s="2">
         <f t="shared" si="4"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2">
-        <f>_xlfn.CONFIDENCE.NORM(C7,C4,C5)</f>
-        <v>1.9599639845400536</v>
-      </c>
-      <c r="D9" s="2">
-        <f>_xlfn.CONFIDENCE.NORM(D7,D4,D5)</f>
-        <v>2.5758293035488999</v>
-      </c>
-      <c r="E9" s="2">
-        <f>_xlfn.CONFIDENCE.NORM(E7,E4,E5)</f>
-        <v>1.6448536269514715</v>
-      </c>
-      <c r="F9" s="2">
-        <f>_xlfn.CONFIDENCE.NORM(F7,F4,F5)</f>
-        <v>0.9799819922700268</v>
-      </c>
-      <c r="G9" s="2">
-        <f>_xlfn.CONFIDENCE.NORM(G7,G4,G5)</f>
         <v>1.28791465177445</v>
       </c>
-      <c r="H9" s="2">
-        <f>_xlfn.CONFIDENCE.NORM(H7,H4,H5)</f>
+      <c r="I11" s="2">
+        <f t="shared" si="4"/>
         <v>0.82242681347573576</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+    <row r="12" spans="3:84" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="2">
-        <f>C8-C9</f>
-        <v>50.040036015459947</v>
-      </c>
-      <c r="D10" s="2">
-        <f t="shared" ref="D10:E10" si="5">D8-D9</f>
-        <v>49.4241706964511</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="D12" s="2">
+        <f>D10-D11</f>
+        <v>49.891887867311802</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" ref="E12:F12" si="5">E10-E11</f>
+        <v>49.276022548302954</v>
+      </c>
+      <c r="F12" s="2">
         <f t="shared" si="5"/>
-        <v>50.355146373048527</v>
-      </c>
-      <c r="F10" s="2">
-        <f t="shared" ref="F10" si="6">F8-F9</f>
-        <v>51.020018007729973</v>
-      </c>
-      <c r="G10" s="2">
-        <f t="shared" ref="G10" si="7">G8-G9</f>
-        <v>50.71208534822555</v>
-      </c>
-      <c r="H10" s="2">
-        <f t="shared" ref="H10" si="8">H8-H9</f>
-        <v>51.177573186524263</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+        <v>50.206998224900381</v>
+      </c>
+      <c r="G12" s="2">
+        <f t="shared" ref="G12" si="6">G10-G11</f>
+        <v>50.871869859581828</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" ref="H12" si="7">H10-H11</f>
+        <v>50.563937200077405</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" ref="I12" si="8">I10-I11</f>
+        <v>51.029425038376118</v>
+      </c>
+    </row>
+    <row r="13" spans="3:84" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="2">
-        <f>C8+C9</f>
-        <v>53.959963984540053</v>
-      </c>
-      <c r="D11" s="2">
-        <f t="shared" ref="D11:H11" si="9">D8+D9</f>
-        <v>54.5758293035489</v>
-      </c>
-      <c r="E11" s="2">
+      <c r="D13" s="2">
+        <f>D10+D11</f>
+        <v>53.811815836391908</v>
+      </c>
+      <c r="E13" s="2">
+        <f t="shared" ref="E13:I13" si="9">E10+E11</f>
+        <v>54.427681155400755</v>
+      </c>
+      <c r="F13" s="2">
         <f t="shared" si="9"/>
-        <v>53.644853626951473</v>
-      </c>
-      <c r="F11" s="2">
+        <v>53.496705478803328</v>
+      </c>
+      <c r="G13" s="2">
         <f t="shared" si="9"/>
-        <v>52.979981992270027</v>
-      </c>
-      <c r="G11" s="2">
+        <v>52.831833844121881</v>
+      </c>
+      <c r="H13" s="2">
         <f t="shared" si="9"/>
-        <v>53.28791465177445</v>
-      </c>
-      <c r="H11" s="2">
+        <v>53.139766503626305</v>
+      </c>
+      <c r="I13" s="2">
         <f t="shared" si="9"/>
-        <v>52.822426813475737</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+        <v>52.674278665327591</v>
+      </c>
+    </row>
+    <row r="15" spans="3:84" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
         <v>12</v>
       </c>
     </row>
